--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF0C9C3-E88D-43B1-B6EF-65051AA89251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1A28C4-B8F1-4F1A-8966-248CA470FF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUITS" sheetId="1" r:id="rId1"/>
     <sheet name="COMMANDES" sheetId="2" r:id="rId2"/>
     <sheet name="PROJETS" sheetId="3" r:id="rId3"/>
     <sheet name="FACTURES" sheetId="4" r:id="rId4"/>
+    <sheet name="Analyse Marketing" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>Code</t>
   </si>
@@ -192,13 +193,41 @@
   </si>
   <si>
     <t>PRJ-104</t>
+  </si>
+  <si>
+    <r>
+      <t>Feuille "UTILISATEURS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> : UserID, Email, Date_Inscription, Pays, Abonnement (Gratuit/Premium)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Feuille "EVENEMENTS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> : UserID, Date_Action, Type_Action (clic, achat, visionnage), Valeur</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +243,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -245,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -256,11 +297,38 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -750,40 +818,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:C6" totalsRowShown="0" headerRowDxfId="7" dataDxfId="8">
-  <autoFilter ref="A1:C6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:D6" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:D6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1225,13 +1296,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC40865-93E0-48F6-9C7E-BD34DA8EACC7}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1241,8 +1312,11 @@
       <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1252,8 +1326,12 @@
       <c r="C2" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <v>Écran 24"</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1263,8 +1341,12 @@
       <c r="C3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <v>Clavier USB</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1274,8 +1356,12 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <v>Webcam HD</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1285,8 +1371,12 @@
       <c r="C5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1295,6 +1385,10 @@
       </c>
       <c r="C6" s="2">
         <v>4</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <v>Souris sans fil</v>
       </c>
     </row>
   </sheetData>
@@ -1470,4 +1564,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA64811-D2DF-4BC4-9E1A-AD5D7821B40A}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1A28C4-B8F1-4F1A-8966-248CA470FF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AEB005-832C-4942-BCA1-95D88CB429BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>Code</t>
   </si>
@@ -222,12 +222,18 @@
       <t> : UserID, Date_Action, Type_Action (clic, achat, visionnage), Valeur</t>
     </r>
   </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Prix Unitai</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,12 +249,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -302,7 +302,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -346,331 +346,383 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -818,28 +870,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:D6" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:D6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="1">
+      <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -847,14 +905,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1296,13 +1354,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC40865-93E0-48F6-9C7E-BD34DA8EACC7}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1315,8 +1374,14 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1330,8 +1395,16 @@
         <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
         <v>Écran 24"</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="1">
+        <f>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <v>149.9</v>
+      </c>
+      <c r="F2" s="1">
+        <f>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</f>
+        <v>299.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1345,8 +1418,16 @@
         <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
         <v>Clavier USB</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="1">
+        <f>_xlfn.XLOOKUP(B3, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <v>25</v>
+      </c>
+      <c r="F3" s="1">
+        <f>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1360,8 +1441,16 @@
         <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
         <v>Webcam HD</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="1">
+        <f>_xlfn.XLOOKUP(B4, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <v>45</v>
+      </c>
+      <c r="F4" s="1">
+        <f>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1375,8 +1464,16 @@
         <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
         <v>Inconnu</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="1">
+        <f>_xlfn.XLOOKUP(B5, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <f>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1389,6 +1486,14 @@
       <c r="D6" s="1" t="str">
         <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
         <v>Souris sans fil</v>
+      </c>
+      <c r="E6" s="1">
+        <f>_xlfn.XLOOKUP(B6, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <v>18.5</v>
+      </c>
+      <c r="F6" s="1">
+        <f>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</f>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AEB005-832C-4942-BCA1-95D88CB429BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CEB223-39BA-41D0-9F3F-4F7DB7A4D9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUITS" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
   <si>
     <t>Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Prix Unitai</t>
+  </si>
+  <si>
+    <t>Cient</t>
   </si>
 </sst>
 </file>
@@ -302,7 +305,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="0"/>
@@ -447,256 +450,459 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -870,33 +1076,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="16">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="8">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="23">
       <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -905,14 +1111,33 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:F4" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
+  <autoFilter ref="A1:F4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1358,6 +1583,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
     <col min="5" max="5" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1392,7 +1618,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
         <v>Écran 24"</v>
       </c>
       <c r="E2" s="1">
@@ -1415,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
         <v>Clavier USB</v>
       </c>
       <c r="E3" s="1">
@@ -1438,7 +1664,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
         <v>Webcam HD</v>
       </c>
       <c r="E4" s="1">
@@ -1461,8 +1687,8 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
-        <v>Inconnu</v>
+        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
+        <v>Arcticle Inconnu</v>
       </c>
       <c r="E5" s="1">
         <f>_xlfn.XLOOKUP(B5, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
@@ -1484,7 +1710,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
         <v>Souris sans fil</v>
       </c>
       <c r="E6" s="1">
@@ -1607,10 +1833,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404800F1-9571-4454-A036-942B9395AA83}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1623,8 +1853,14 @@
       <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
@@ -1637,8 +1873,16 @@
       <c r="D2" s="2">
         <v>4500</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
+        <v>Alpha</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
+        <v>Terminé</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -1651,8 +1895,16 @@
       <c r="D3" s="2">
         <v>1600</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
+        <v>Beta</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
+        <v>En cours</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1665,9 +1917,20 @@
       <c r="D4" s="2">
         <v>2200</v>
       </c>
+      <c r="E4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
+        <v>Non Identifié</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
+        <v>Non Classifié</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CEB223-39BA-41D0-9F3F-4F7DB7A4D9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C53C735-7CA3-4DCE-928B-A287805E4569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>Code</t>
   </si>
@@ -231,12 +231,15 @@
   <si>
     <t>Cient</t>
   </si>
+  <si>
+    <t>Reste à Facturer</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +264,12 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -289,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -301,11 +310,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -349,6 +361,181 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -375,31 +562,385 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -451,509 +992,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1090,19 +1128,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="24">
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="23">
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="8">
       <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1111,32 +1149,35 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:F4" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
-  <autoFilter ref="A1:F4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:G4" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A1:G4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut" dataDxfId="23">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1735,7 +1776,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1833,14 +1874,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404800F1-9571-4454-A036-942B9395AA83}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1859,8 +1902,11 @@
       <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>47</v>
       </c>
@@ -1881,8 +1927,13 @@
         <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
         <v>Terminé</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="1">
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -1903,8 +1954,12 @@
         <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
         <v>En cours</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="1">
+        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F3,FACTURES!D:D)</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1924,6 +1979,10 @@
       <c r="F4" s="1" t="str">
         <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
         <v>Non Classifié</v>
+      </c>
+      <c r="G4" s="1">
+        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!B:B,F2,FACTURES!D:D)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C53C735-7CA3-4DCE-928B-A287805E4569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFE6ABF-786F-4CD9-9A9E-42DD98F44E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUITS" sheetId="1" r:id="rId1"/>
@@ -361,181 +361,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -588,307 +413,482 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1114,33 +1114,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="10">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="9">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="2">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!D:D,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="1">
       <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1149,14 +1149,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1176,7 +1176,7 @@
     <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut" dataDxfId="23">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="22">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1659,11 +1659,11 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</f>
         <v>Écran 24"</v>
       </c>
       <c r="E2" s="1">
-        <f>_xlfn.XLOOKUP(B2, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <f>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!D:D,0)</f>
         <v>149.9</v>
       </c>
       <c r="F2" s="1">
@@ -1682,11 +1682,11 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</f>
         <v>Clavier USB</v>
       </c>
       <c r="E3" s="1">
-        <f>_xlfn.XLOOKUP(B3, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <f>_xlfn.XLOOKUP(B3,PRODUITS!A:A,PRODUITS!D:D,0)</f>
         <v>25</v>
       </c>
       <c r="F3" s="1">
@@ -1705,11 +1705,11 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</f>
         <v>Webcam HD</v>
       </c>
       <c r="E4" s="1">
-        <f>_xlfn.XLOOKUP(B4, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <f>_xlfn.XLOOKUP(B4,PRODUITS!A:A,PRODUITS!D:D,0)</f>
         <v>45</v>
       </c>
       <c r="F4" s="1">
@@ -1728,11 +1728,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
-        <v>Arcticle Inconnu</v>
+        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</f>
+        <v>Article Inconnu</v>
       </c>
       <c r="E5" s="1">
-        <f>_xlfn.XLOOKUP(B5, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <f>_xlfn.XLOOKUP(B5,PRODUITS!A:A,PRODUITS!D:D,0)</f>
         <v>0</v>
       </c>
       <c r="F5" s="1">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1751,11 +1751,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Arcticle Inconnu")</f>
+        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</f>
         <v>Souris sans fil</v>
       </c>
       <c r="E6" s="1">
-        <f>_xlfn.XLOOKUP(B6, PRODUITS!A:A, PRODUITS!D:D, 0)</f>
+        <f>_xlfn.XLOOKUP(B6,PRODUITS!A:A,PRODUITS!D:D,0)</f>
         <v>18.5</v>
       </c>
       <c r="F6" s="1">

--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFE6ABF-786F-4CD9-9A9E-42DD98F44E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6D6DAD-2B1B-480A-B4CE-2072B575E838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUITS" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>Reste à Facturer</t>
+  </si>
+  <si>
+    <t>Statut Projet</t>
+  </si>
+  <si>
+    <t>Projet</t>
   </si>
 </sst>
 </file>
@@ -298,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -313,11 +319,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="32">
     <dxf>
       <font>
         <b val="0"/>
@@ -413,481 +422,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -914,6 +448,507 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -966,32 +1001,32 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1114,33 +1149,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="26">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="25">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!D:D,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="24">
       <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1149,35 +1184,38 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:G4" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:G4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="24">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:H4" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="2">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Client Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut" dataDxfId="23">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut Projet" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Statut Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="22">
+    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{441844BA-20F8-4D3F-AD8F-7723346E62BD}" name="Projet" dataDxfId="0">
+      <calculatedColumnFormula>IF(OR(F2="Terminé", F2="Annulé"),"⚠️ Projet clôturé","En cours")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1880,10 +1918,11 @@
     <col min="1" max="1" width="12.109375" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
     <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1900,10 +1939,13 @@
         <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1920,16 +1962,20 @@
         <v>4500</v>
       </c>
       <c r="E2" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Client Inconnu")</f>
         <v>Alpha</v>
       </c>
       <c r="F2" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Statut Inconnu")</f>
         <v>Terminé</v>
       </c>
       <c r="G2" s="1">
-        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</f>
+        <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(F:F,"Terminé",D:D)</f>
         <v>0</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <f t="shared" ref="H2:H4" si="0">IF(OR(F2="Terminé", F2="Annulé"),"⚠️ Projet clôturé","En cours")</f>
+        <v>⚠️ Projet clôturé</v>
       </c>
       <c r="K2" s="5"/>
     </row>
@@ -1947,19 +1993,23 @@
         <v>1600</v>
       </c>
       <c r="E3" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
+        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!B:B,"Client Inconnu")</f>
         <v>Beta</v>
       </c>
       <c r="F3" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
+        <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!E:E,"Statut Inconnu")</f>
         <v>En cours</v>
       </c>
       <c r="G3" s="1">
         <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F3,FACTURES!D:D)</f>
         <v>1600</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H3" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>En cours</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1973,16 +2023,20 @@
         <v>2200</v>
       </c>
       <c r="E4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!B:B,"Non Identifié")</f>
-        <v>Non Identifié</v>
+        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!B:B,"Client Inconnu")</f>
+        <v>Client Inconnu</v>
       </c>
       <c r="F4" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!E:E,"Non Classifié")</f>
-        <v>Non Classifié</v>
+        <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!E:E,"Statut Inconnu")</f>
+        <v>Statut Inconnu</v>
       </c>
       <c r="G4" s="1">
         <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!B:B,F2,FACTURES!D:D)</f>
         <v>0</v>
+      </c>
+      <c r="H4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>En cours</v>
       </c>
     </row>
   </sheetData>

--- a/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
+++ b/phase-1-excel-avance/exercices/RECHERCHEX.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\excel-ai-journey\phase-1-excel-avance\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6D6DAD-2B1B-480A-B4CE-2072B575E838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9238F8-9632-469C-BDF6-12C4567817CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{F1A20F38-2A4F-451B-B6F6-D18EC979FF5A}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUITS" sheetId="1" r:id="rId1"/>
     <sheet name="COMMANDES" sheetId="2" r:id="rId2"/>
     <sheet name="PROJETS" sheetId="3" r:id="rId3"/>
     <sheet name="FACTURES" sheetId="4" r:id="rId4"/>
-    <sheet name="Analyse Marketing" sheetId="5" r:id="rId5"/>
+    <sheet name="UTILISATEURS" sheetId="5" r:id="rId5"/>
+    <sheet name="EVENEMENTS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t>Code</t>
   </si>
@@ -195,34 +196,6 @@
     <t>PRJ-104</t>
   </si>
   <si>
-    <r>
-      <t>Feuille "UTILISATEURS"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> : UserID, Email, Date_Inscription, Pays, Abonnement (Gratuit/Premium)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Feuille "EVENEMENTS"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> : UserID, Date_Action, Type_Action (clic, achat, visionnage), Valeur</t>
-    </r>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -239,13 +212,70 @@
   </si>
   <si>
     <t>Projet</t>
+  </si>
+  <si>
+    <t>UserID</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Date_Inscription</t>
+  </si>
+  <si>
+    <t>Pays</t>
+  </si>
+  <si>
+    <t>Abonnement</t>
+  </si>
+  <si>
+    <t>Date_Action</t>
+  </si>
+  <si>
+    <t>Type_Action</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>ID-1</t>
+  </si>
+  <si>
+    <t>ID-2</t>
+  </si>
+  <si>
+    <t>ID-3</t>
+  </si>
+  <si>
+    <t>ID-4</t>
+  </si>
+  <si>
+    <t>ID-5</t>
+  </si>
+  <si>
+    <t>ID-6</t>
+  </si>
+  <si>
+    <t>ID-7</t>
+  </si>
+  <si>
+    <t>ID-8</t>
+  </si>
+  <si>
+    <t>ID-9</t>
+  </si>
+  <si>
+    <t>ID-10</t>
+  </si>
+  <si>
+    <t>bozy.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +307,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -304,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -319,9 +355,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -344,6 +377,181 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -422,6 +630,306 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -448,6 +956,84 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -474,559 +1060,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF0F1115"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1149,33 +1182,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}" name="Tableau1" displayName="Tableau1" ref="A1:E6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:E6" xr:uid="{90EDE2C6-7AF7-4BAF-82D7-5D20E6BE793E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{D229C281-9921-44DA-8ADF-2BBF174D448C}" name="Code" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{329C4A42-FDFB-426D-A39F-6BF25703E85C}" name="Désignation" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{EC89EC55-A0B2-47BC-ADFE-6BF88C9FCA42}" name="Catégorie" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{56ADE8FF-2F4A-407C-949A-434522EFC0DF}" name="Prix_Unité" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{90E1DEAE-B2F5-4396-A877-17964625C319}" name="Stock" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}" name="Tableau2" displayName="Tableau2" ref="A1:F6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:F6" xr:uid="{77BCDC36-CC41-4316-8477-40C0AF984E3C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{742C9074-A44B-4564-9109-4D96F296B411}" name="N° Cde" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{A2E4C4D0-A8C1-4188-B1EA-885E977D2AD2}" name="Code_Article" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{BBCFCE8B-0E9C-411D-966A-4B9BE6944EC4}" name="Quantité" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8DA8A676-86A2-4CA1-BE0E-24702F6148B1}" name="Désignation" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!B:B,"Article Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="25">
+    <tableColumn id="5" xr3:uid="{AFB335E0-9805-47AE-A890-299A2DE0AB1B}" name="Prix Unitai" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PRODUITS!A:A,PRODUITS!D:D,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{F2E78198-992D-4F6C-A878-B11926E0A8BA}" name="Total" dataDxfId="7">
       <calculatedColumnFormula>Tableau2[[#This Row],[Quantité]]*Tableau2[[#This Row],[Prix Unitai]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1184,37 +1217,37 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}" name="Tableau3" displayName="Tableau3" ref="A1:E5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E5" xr:uid="{4E1EBF1E-6DCA-4D04-AC75-D39959706213}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{B5568E22-E874-4844-A90D-4D19748F2760}" name="ID_Projet" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{AB036400-2BCD-492D-8CF4-8FC7A0BCBEA4}" name="Client" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F0CC70DE-97A6-42FB-B377-AC5570A96FFE}" name="Type" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{50E2533C-4F1E-4CED-A492-F9A6A554481B}" name="Budget_HT" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{9AFB5181-2E05-4F02-A38E-BD00E0BA70C7}" name="Statut" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:H4" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}" name="Tableau4" displayName="Tableau4" ref="A1:H4" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:H4" xr:uid="{598CC453-BA4A-4B93-9677-D3601A5FB97B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{1E259E25-3161-47E0-A018-8E0F70CDE580}" name="N° Facture" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{3A2EEB15-BC71-46C5-9701-E13263A52FA8}" name="ID_Projet" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{CD2854B4-0546-42F0-9E52-F9A389F7F8BA}" name="Date" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{CB0B43F0-A9DD-4511-926F-64A93F456B4C}" name="Montant_HT" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9D814BDE-B4C5-4A74-A5E2-63E9B58E97B2}" name="Cient" dataDxfId="25">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!B:B,"Client Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut Projet" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{8821E84F-EC42-4EE8-86F2-511E2897E8A6}" name="Statut Projet" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!E:E,"Statut Inconnu")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{70C5FF4B-049C-429F-9AAB-F9E3D6AA10FF}" name="Reste à Facturer" dataDxfId="23">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F2,FACTURES!D:D)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{441844BA-20F8-4D3F-AD8F-7723346E62BD}" name="Projet" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{441844BA-20F8-4D3F-AD8F-7723346E62BD}" name="Projet" dataDxfId="22">
       <calculatedColumnFormula>IF(OR(F2="Terminé", F2="Annulé"),"⚠️ Projet clôturé","En cours")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1680,10 +1713,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1936,16 +1969,16 @@
         <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1973,7 +2006,7 @@
         <f>_xlfn.XLOOKUP(B2,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(F:F,"Terminé",D:D)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="1" t="str">
         <f t="shared" ref="H2:H4" si="0">IF(OR(F2="Terminé", F2="Annulé"),"⚠️ Projet clôturé","En cours")</f>
         <v>⚠️ Projet clôturé</v>
       </c>
@@ -2004,7 +2037,7 @@
         <f>_xlfn.XLOOKUP(B3,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!F:F,F3,FACTURES!D:D)</f>
         <v>1600</v>
       </c>
-      <c r="H3" s="6" t="str">
+      <c r="H3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>En cours</v>
       </c>
@@ -2034,7 +2067,7 @@
         <f>_xlfn.XLOOKUP(B4,PROJETS!A:A,PROJETS!D:D,0)-SUMIF(FACTURES!B:B,F2,FACTURES!D:D)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>En cours</v>
       </c>
@@ -2049,17 +2082,102 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA64811-D2DF-4BC4-9E1A-AD5D7821B40A}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225DF998-6947-4255-9DCD-599893D5E181}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
